--- a/baltimore-figures/results/Results List.xlsx
+++ b/baltimore-figures/results/Results List.xlsx
@@ -1,19 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e6c040798b5cdcf/Documents/School/Project/air-pollution-data/baltimore-figures/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_F25DC773A252ABDACC10480A99DC570A5ADE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4237169A-BB53-4A11-AC60-95CDCB24D419}"/>
+  <xr:revisionPtr revIDLastSave="189" documentId="11_F25DC773A252ABDACC10480A99DC570A5ADE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EAAAC2C-5BC7-44B9-A862-71DCFFAB1F0F}"/>
   <bookViews>
-    <workbookView xWindow="31800" yWindow="3075" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="4350" yWindow="1290" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="2026-06-21" sheetId="1" r:id="rId1"/>
+    <sheet name="Ansatz 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Ansatz 2" sheetId="2" r:id="rId2"/>
+    <sheet name="Ansatz 3" sheetId="3" r:id="rId3"/>
+    <sheet name="Ansatz 4" sheetId="4" r:id="rId4"/>
+    <sheet name="Ansatz 5" sheetId="5" r:id="rId5"/>
+    <sheet name="Ansatz 6" sheetId="6" r:id="rId6"/>
+    <sheet name="Ansatz 7" sheetId="8" r:id="rId7"/>
+    <sheet name="Sheet4" sheetId="7" r:id="rId8"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="104">
   <si>
     <t>qnn_cnotlist =  [ [0,2,1],[1,2], [2,0],[0, 1],[0,1,2] ]</t>
   </si>
@@ -67,6 +74,276 @@
   </si>
   <si>
     <t>[1.60860577 5.90834007 6.43847897 3.13721595 0.83939961 1.73486228]</t>
+  </si>
+  <si>
+    <t>[ 2.35814112  3.72909937  4.82462467  3.16814564  3.61493908 -2.6869376 ]</t>
+  </si>
+  <si>
+    <t>[2.48890498 3.18078239 5.10076867 3.25149716 0.50568863 0.30664817]</t>
+  </si>
+  <si>
+    <t>[2.49131158 3.18630182 5.0896909  3.24895262 0.51190608 0.30567002]</t>
+  </si>
+  <si>
+    <t>[2.70956689 3.28883981 4.99752154 3.39024802 0.49863449 0.35028418]</t>
+  </si>
+  <si>
+    <t>[2.80603347 3.15415495 4.94774745 3.42808247 0.5147857  0.24307702]</t>
+  </si>
+  <si>
+    <t>[2.48424406 3.19387286 5.07536173 3.24812697 0.51889724 0.2990401 ]</t>
+  </si>
+  <si>
+    <t>[2.51432358 3.20188038 4.94400747 3.3553017  0.49908853 0.33837483]</t>
+  </si>
+  <si>
+    <t>[2.80588474 3.17138625 4.93543093 3.45712318 0.59015906 0.22855714]</t>
+  </si>
+  <si>
+    <t>[2.8057307  3.17167117 4.93563378 3.45702767 0.59023683 0.22857668]</t>
+  </si>
+  <si>
+    <t>[2.90173146 3.20939114 4.91849103 3.41999108 0.59916677 0.23337052]</t>
+  </si>
+  <si>
+    <t>qnn_cnot_list = [[0], [0,1,2], [2,1],[1,0]]</t>
+  </si>
+  <si>
+    <t>[3.12607599 3.207105   4.88525753 3.39831886 0.56593683 0.19482986]</t>
+  </si>
+  <si>
+    <t>[3.00628847 3.15432998 4.9485119 3.47150325 0.64141536 0.15220963]</t>
+  </si>
+  <si>
+    <t>Epochs</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Epocs</t>
+  </si>
+  <si>
+    <t>qnn_cnot_list = [ [0,1], [1,2], [2,1,0], [0,1,2]]</t>
+  </si>
+  <si>
+    <t>[19.24124015 13.29055563  6.34964183  5.4730771  -3.20482449  1.03181804]</t>
+  </si>
+  <si>
+    <t>[ 4.23869784  6.74837616  3.29623597  3.94970953 -0.03421962  0.9286688 ]</t>
+  </si>
+  <si>
+    <t>[ 0.33384169  6.33607267  4.01399363  5.2642326  -0.10653273  1.58727756]</t>
+  </si>
+  <si>
+    <t>[ 3.43604956  6.19018649  4.03701368  4.11898353 -0.01147159  1.61762166]</t>
+  </si>
+  <si>
+    <t>[3.27690475 6.2883565  3.99754689 4.10796573 0.04118601 1.55095362]</t>
+  </si>
+  <si>
+    <t>[ 4.15788729  6.50179218  3.52106338  4.00824315 -0.11845519  0.9931989 ]</t>
+  </si>
+  <si>
+    <t>[ 3.30035483  6.25604524  3.87335084  4.19407761 -0.10550864  1.79514577]</t>
+  </si>
+  <si>
+    <t>[ 3.16845094  6.13900308  3.90595557  3.89717615 -0.04435891  1.37472341]</t>
+  </si>
+  <si>
+    <t>[ 2.97176088  5.80021566  3.58697358  3.80422379 -0.16922497  1.11959504]</t>
+  </si>
+  <si>
+    <t>[ 3.17527473  6.18953421  3.89573244  3.90839154 -0.02916905  1.39469476]</t>
+  </si>
+  <si>
+    <t>qnn_cnot_list = [[0,1],[1,2],[2,0]]</t>
+  </si>
+  <si>
+    <t>[13.43258438 12.62157722  5.30544459  3.84698844  0.70237461 -0.69190291]</t>
+  </si>
+  <si>
+    <t>[-2.63795785  6.45399866  4.50974906  2.63454398 -0.01115377  0.14174962]</t>
+  </si>
+  <si>
+    <t>[3.59804728 6.39576667 4.4712246  2.62467808 0.01228265 0.13147958]</t>
+  </si>
+  <si>
+    <t>[ 3.38857855  6.02578685  4.35302733  2.6282017  -0.00991599  0.09679049]</t>
+  </si>
+  <si>
+    <t>[3.24212617 6.13628873 4.37252185 2.66932581 0.03362474 0.10358148]</t>
+  </si>
+  <si>
+    <t>[3.57761049 6.39249404 4.45232743 2.61909368 0.01831866 0.13021806]</t>
+  </si>
+  <si>
+    <t>[ 3.46611879  6.2277411   4.39536472  2.62234104 -0.05058082  0.12641931]</t>
+  </si>
+  <si>
+    <t>[ 3.15451039  6.12723492  4.34966236  2.6500647  -0.0456279   0.01253917]</t>
+  </si>
+  <si>
+    <t>[ 3.15438425  6.12695202  4.34928043  2.64985704 -0.04555892  0.01255656]</t>
+  </si>
+  <si>
+    <t>[ 3.09384943e+00  6.11850690e+00  4.36444448e+00  2.64088796e+00  -3.53255474e-02 -6.03910148e-03]</t>
+  </si>
+  <si>
+    <t>[3.09943617 3.16119519 4.87028799 3.2558707  0.53620447 0.05853435]</t>
+  </si>
+  <si>
+    <t>qnn_cnotlist =  [ [0,2,1],[1,2], [2,0],[0, 1] ]</t>
+  </si>
+  <si>
+    <t>[21.13108141  7.53405092  7.77819922  4.17021329  0.47977537 -3.68199831]</t>
+  </si>
+  <si>
+    <t>[ 0.99766037  3.97210264  4.72465725  3.60562699 -0.30653697  1.15891751]</t>
+  </si>
+  <si>
+    <t>[ 0.57122996  4.82172545  4.76202915  4.23450635 -0.65537911  0.49954461]</t>
+  </si>
+  <si>
+    <t>[1.32898242 4.31452219 4.61475386 3.69570945 0.04660039 1.06449158]</t>
+  </si>
+  <si>
+    <t>[ 1.22532313  4.36701183  4.56285557  3.7070959  -0.10334274  0.9870052 ]</t>
+  </si>
+  <si>
+    <t>[ 0.98715439  3.95167187  4.73043977  3.59767777 -0.31908489  1.15343059]</t>
+  </si>
+  <si>
+    <t>[1.43422334 4.46289699 4.64562813 3.84518025 0.08190897 1.08091753]</t>
+  </si>
+  <si>
+    <t>[ 1.35831009  4.34693268  4.45161561  3.6274475  -0.08973818  1.00860953]</t>
+  </si>
+  <si>
+    <t>[ 1.45030251  4.76556922  5.06589918  4.08598568 -0.04884631  0.52099047]</t>
+  </si>
+  <si>
+    <t>[ 1.53545921  4.82187512  5.07439687  4.10262107 -0.02578723  0.50516035]</t>
+  </si>
+  <si>
+    <t>[ 1.45856119  4.52660618  4.32418723  3.75375183 -0.08546368  1.06646626]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qnn_cnot_list = [[1,2], [2,0],[0, 1],] </t>
+  </si>
+  <si>
+    <t>[5.30130975 7.09676257 4.6929188  4.05873686 2.3364946  2.7908295 ]</t>
+  </si>
+  <si>
+    <t>[1.80355417 4.51699687 4.67792031 4.237265   0.54364211 0.6971558 ]</t>
+  </si>
+  <si>
+    <t>[1.81834615 4.51446779 4.68123597 4.23997185 0.55125694 0.69398609]</t>
+  </si>
+  <si>
+    <t>[1.5989941  4.50169912 4.70267059 3.96654988 0.40418793 0.81626675]</t>
+  </si>
+  <si>
+    <t>[1.44912703 4.64850639 4.68916572 3.90690296 0.31663814 0.8048743 ]</t>
+  </si>
+  <si>
+    <t>[1.71156824 4.62635457 4.71812524 4.14175271 0.50587663 0.80807854]</t>
+  </si>
+  <si>
+    <t>[1.76210726 4.62546714 4.71718098 4.12575098 0.41599913 0.82021369]</t>
+  </si>
+  <si>
+    <t>[1.56736601 4.57735161 4.72752306 3.87714633 0.43799214 0.72894343]</t>
+  </si>
+  <si>
+    <t>[1.56775478 4.5766333  4.72817356 3.87669566 0.43785798 0.72918533]</t>
+  </si>
+  <si>
+    <t>[1.56191747 4.60515969 4.70417744 3.8679271  0.45469809 0.73092696]</t>
+  </si>
+  <si>
+    <t>[ 4.88589578  4.62768957  4.71495184  2.16649328  0.41030989 -0.82674265]</t>
+  </si>
+  <si>
+    <t>[ 1.57370634  4.71894275  4.70760585  2.41167962  0.43734421 -0.73097023]</t>
+  </si>
+  <si>
+    <t>[ 4.95031621  4.51634889  4.6980377   2.04491034  0.54687708 -0.69305399]</t>
+  </si>
+  <si>
+    <t>[ 4.70357831  4.60496675  4.70166675  2.41549254  0.45424972 -0.73160598]</t>
+  </si>
+  <si>
+    <t>qnn_cnot_list = [[0,2,1],[1,2], [2,1,0],[0, 1],[1,2]]</t>
+  </si>
+  <si>
+    <t>[21.70430034  5.42162724  9.86876111  2.2054185  -0.88141909 -4.90454765]</t>
+  </si>
+  <si>
+    <t>[ 4.2045319   5.09496549  6.08250344  0.47683679  1.39048451 -0.94071242]</t>
+  </si>
+  <si>
+    <t>[ 4.19955259  5.09306936  6.08079535  0.48284826  1.39800635 -0.93833073]</t>
+  </si>
+  <si>
+    <t>[ 3.61195983  5.6381229   3.16581092  3.19351204 -1.53948338  1.21358238]</t>
+  </si>
+  <si>
+    <t>[3.91981126 5.33663296 6.21784276 2.97703296 1.62895464 1.39529211]</t>
+  </si>
+  <si>
+    <t>[ 4.19600432  5.08853695  6.08296013  0.4720031   1.39533112 -0.94100546]</t>
+  </si>
+  <si>
+    <t>[ 3.66010029  5.6226945   3.09430124  3.25383721  1.64949942 -1.9153936 ]</t>
+  </si>
+  <si>
+    <t>[ 2.67121752  5.91266954  3.69369619  2.60558195 -1.07548831  0.66898018]</t>
+  </si>
+  <si>
+    <t>[ 3.61582429  5.52610579  3.18165757  3.01577031 -1.66646549  1.11735261]</t>
+  </si>
+  <si>
+    <t>[ 2.54917573  5.9408244   3.71871672  2.40425074 -1.01052673  0.6018926 ]</t>
+  </si>
+  <si>
+    <t>[ 3.71112705  5.50651268  3.18659181  2.95210124 -1.76691557  1.14449389]</t>
+  </si>
+  <si>
+    <t>`</t>
+  </si>
+  <si>
+    <t>[23.22034035 16.78588125  8.45527752  2.93847062  0.68454492  3.77739611]</t>
+  </si>
+  <si>
+    <t>[ 8.85350045  9.81777488  9.86369812  1.83871503 -3.07801249  1.81764629]</t>
+  </si>
+  <si>
+    <t>[-0.74404048  9.6759413   7.84244738  3.34559329 -0.59496223  3.79911906]</t>
+  </si>
+  <si>
+    <t>[ 7.11074585  4.82101261  6.72084649  4.57829865  0.12040011 -1.61124752]</t>
+  </si>
+  <si>
+    <t>[ 4.1806346   8.57102971  5.95512213  2.04043495 -0.14594123  1.41437259]</t>
+  </si>
+  <si>
+    <t>[2.14631839 7.06862494 6.73715099 3.69026907 1.57371574 1.94866676]</t>
+  </si>
+  <si>
+    <t>[ 4.53386306  8.46971657  5.75608367  2.08817921 -0.20169847  1.27840128]</t>
+  </si>
+  <si>
+    <t>[3.21275522 9.41126155 4.96768343 3.07478758 0.01247164 0.25120832]</t>
+  </si>
+  <si>
+    <t>[ 4.81660601  5.13554628  4.71674361  3.08209821 -0.64112618 -0.66412069]</t>
+  </si>
+  <si>
+    <t>[ 3.36683965  6.126464    4.33003854  3.1992968   0.14940535 -0.37139982]</t>
+  </si>
+  <si>
+    <t>qnn_cnot_list = [[0,2,1], [1,2], [2,1,0],[0, 1],[0,1,2]] #Ansatz 8</t>
   </si>
 </sst>
 </file>
@@ -88,12 +365,18 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -108,11 +391,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -128,6 +413,402 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62634A2E-7D43-9896-6B96-923495F49121}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7000875" y="381000"/>
+          <a:ext cx="5362575" cy="2266950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D90664B-2F81-878D-96EE-1B705AB2D9D9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7600950" y="628650"/>
+          <a:ext cx="4743450" cy="2266950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7CA26B5-29A5-79D1-AB29-60AC2FAF7DBE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3657600" y="571500"/>
+          <a:ext cx="4743450" cy="2266950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>72390</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AB91E48-969B-F5E5-F34B-6FDAB8E79C24}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7680960" y="365760"/>
+          <a:ext cx="4133850" cy="2266950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>72390</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BCC3EA58-8275-8A89-DB4E-8118171FF560}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4876800" y="548640"/>
+          <a:ext cx="4743450" cy="2266950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>72390</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F301BA58-B213-152C-EB14-6A8502EBC6B3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4267200" y="548640"/>
+          <a:ext cx="4133850" cy="2266950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>72390</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{64A0FD7E-4283-6ED3-B40A-F6FE25A0F9D6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4267200" y="548640"/>
+          <a:ext cx="5362575" cy="2266950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84C8152B-8F6C-8A39-AC5D-BDDAA13CAEC4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4324350" y="762000"/>
+          <a:ext cx="5362575" cy="2266950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -393,13 +1074,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="67.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -409,11 +1092,17 @@
       <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>100</v>
       </c>
@@ -423,8 +1112,14 @@
       <c r="C2">
         <v>0.55649999999999999</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>46194</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>200</v>
       </c>
@@ -434,8 +1129,14 @@
       <c r="C3">
         <v>0.60050000000000003</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2">
+        <v>46194</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>300</v>
       </c>
@@ -445,8 +1146,14 @@
       <c r="C4">
         <v>0.60099999999999998</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2">
+        <v>46194</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>400</v>
       </c>
@@ -456,8 +1163,14 @@
       <c r="C5">
         <v>0.61850000000000005</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2">
+        <v>46194</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>500</v>
       </c>
@@ -467,8 +1180,14 @@
       <c r="C6">
         <v>0.68300000000000005</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>46194</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>600</v>
       </c>
@@ -478,19 +1197,31 @@
       <c r="C7">
         <v>0.68100000000000005</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46194</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>700</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="3">
         <v>0.69599999999999995</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2">
+        <v>46194</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>800</v>
       </c>
@@ -500,8 +1231,14 @@
       <c r="C9">
         <v>0.67200000000000004</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2">
+        <v>46194</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>900</v>
       </c>
@@ -511,8 +1248,14 @@
       <c r="C10">
         <v>0.67200000000000004</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2">
+        <v>46194</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>1000</v>
       </c>
@@ -521,10 +1264,1614 @@
       </c>
       <c r="C11">
         <v>0.60250000000000004</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2">
+        <v>46194</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>650</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12">
+        <v>0.64200000000000002</v>
+      </c>
+      <c r="D12">
+        <v>5</v>
+      </c>
+      <c r="E12" s="2">
+        <v>46194</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2FB9B58-3F5C-47D6-B340-E8638D04E47D}">
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="66.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>100</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2">
+        <v>0.67100000000000004</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>46195</v>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>200</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>0.64200000000000002</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2">
+        <v>46195</v>
+      </c>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>300</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4">
+        <v>0.64149999999999996</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2">
+        <v>46195</v>
+      </c>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>400</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5">
+        <v>0.68049999999999999</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2">
+        <v>46195</v>
+      </c>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>500</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6">
+        <v>0.68300000000000005</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>46195</v>
+      </c>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>600</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7">
+        <v>0.64249999999999996</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46195</v>
+      </c>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>700</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8">
+        <v>0.65549999999999997</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2">
+        <v>46195</v>
+      </c>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>800</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9">
+        <v>0.6875</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2">
+        <v>46195</v>
+      </c>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>900</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10">
+        <v>0.6875</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2">
+        <v>46195</v>
+      </c>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1000</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0.6905</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2">
+        <v>46195</v>
+      </c>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>1100</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12">
+        <v>0.65600000000000003</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2">
+        <v>46195</v>
+      </c>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>1000</v>
+      </c>
+      <c r="B13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13">
+        <v>0.6905</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+      <c r="E13" s="2">
+        <v>46197</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BC95A88-6095-4650-A115-205860F36A14}">
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="66.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>100</v>
+      </c>
+      <c r="B2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2">
+        <v>0.59650000000000003</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>100</v>
+      </c>
+      <c r="B3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3">
+        <v>0.58050000000000002</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>200</v>
+      </c>
+      <c r="B4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4">
+        <v>0.64649999999999996</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>300</v>
+      </c>
+      <c r="B5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5">
+        <v>0.65249999999999997</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>400</v>
+      </c>
+      <c r="B6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.69650000000000001</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>500</v>
+      </c>
+      <c r="B7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7">
+        <v>0.67849999999999999</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>600</v>
+      </c>
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8">
+        <v>0.65100000000000002</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>700</v>
+      </c>
+      <c r="B9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9">
+        <v>0.67249999999999999</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>800</v>
+      </c>
+      <c r="B10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10">
+        <v>0.68799999999999994</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>900</v>
+      </c>
+      <c r="B11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11">
+        <v>0.68799999999999994</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>1000</v>
+      </c>
+      <c r="B12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12">
+        <v>0.69099999999999995</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2">
+        <v>46197</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{598333DE-D8CD-4734-A69C-916F2F5762FB}">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="66.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>100</v>
+      </c>
+      <c r="B2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2">
+        <v>0.59650000000000003</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>200</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3">
+        <v>0.61499999999999999</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>300</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4">
+        <v>0.59150000000000003</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>400</v>
+      </c>
+      <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5">
+        <v>0.60750000000000004</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>500</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6">
+        <v>0.60299999999999998</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>600</v>
+      </c>
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7">
+        <v>0.61950000000000005</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>700</v>
+      </c>
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8">
+        <v>0.60250000000000004</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>800</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9">
+        <v>0.61850000000000005</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>900</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10">
+        <v>0.621</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1000</v>
+      </c>
+      <c r="B11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11">
+        <v>0.61550000000000005</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2">
+        <v>46197</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E44278B7-9714-423A-B064-505511710EA5}">
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="66.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>100</v>
+      </c>
+      <c r="B2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2">
+        <v>0.68600000000000005</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>200</v>
+      </c>
+      <c r="B3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3">
+        <v>0.63649999999999995</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>300</v>
+      </c>
+      <c r="B4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4">
+        <v>0.61250000000000004</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>400</v>
+      </c>
+      <c r="B5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5">
+        <v>0.65349999999999997</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>500</v>
+      </c>
+      <c r="B6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6">
+        <v>0.66300000000000003</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>600</v>
+      </c>
+      <c r="B7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7">
+        <v>0.63449999999999995</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>700</v>
+      </c>
+      <c r="B8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8">
+        <v>0.63400000000000001</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>800</v>
+      </c>
+      <c r="B9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0.67100000000000004</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>900</v>
+      </c>
+      <c r="B10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10">
+        <v>0.65700000000000003</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1000</v>
+      </c>
+      <c r="B11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11">
+        <v>0.65549999999999997</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>800</v>
+      </c>
+      <c r="B12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12">
+        <v>0.67100000000000004</v>
+      </c>
+      <c r="D12">
+        <v>5</v>
+      </c>
+      <c r="E12" s="2">
+        <v>46198</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5497ED71-FB54-4304-8013-DD634A2B86A5}">
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="66.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>100</v>
+      </c>
+      <c r="B2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2">
+        <v>0.63800000000000001</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>46198</v>
+      </c>
+      <c r="I2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>200</v>
+      </c>
+      <c r="B3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3">
+        <v>0.66149999999999998</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>300</v>
+      </c>
+      <c r="B4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4">
+        <v>0.66</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>400</v>
+      </c>
+      <c r="B5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5">
+        <v>0.68049999999999999</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>500</v>
+      </c>
+      <c r="B6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6">
+        <v>0.67949999999999999</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>600</v>
+      </c>
+      <c r="B7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7">
+        <v>0.66749999999999998</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>700</v>
+      </c>
+      <c r="B8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8">
+        <v>0.66300000000000003</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>800</v>
+      </c>
+      <c r="B9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9">
+        <v>0.6825</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>900</v>
+      </c>
+      <c r="B10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10">
+        <v>0.6825</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1000</v>
+      </c>
+      <c r="B11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11">
+        <v>0.6835</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>1100</v>
+      </c>
+      <c r="B12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12">
+        <v>0.66149999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>1200</v>
+      </c>
+      <c r="B13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13">
+        <v>0.68300000000000005</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>1300</v>
+      </c>
+      <c r="B14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14">
+        <v>0.66200000000000003</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>1400</v>
+      </c>
+      <c r="B15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15">
+        <v>0.6835</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{393F2789-7505-4E66-B7B5-33F183F1F61A}">
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="66.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>100</v>
+      </c>
+      <c r="B2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2">
+        <v>0.54649999999999999</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>200</v>
+      </c>
+      <c r="B3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3">
+        <v>0.60750000000000004</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>300</v>
+      </c>
+      <c r="B4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4">
+        <v>0.60850000000000004</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>400</v>
+      </c>
+      <c r="B5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.66600000000000004</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>500</v>
+      </c>
+      <c r="B6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6">
+        <v>0.63600000000000001</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>600</v>
+      </c>
+      <c r="B7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7">
+        <v>0.60750000000000004</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>700</v>
+      </c>
+      <c r="B8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8">
+        <v>0.65749999999999997</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>800</v>
+      </c>
+      <c r="B9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9">
+        <v>0.60750000000000004</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>900</v>
+      </c>
+      <c r="B10" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10">
+        <v>0.65549999999999997</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1000</v>
+      </c>
+      <c r="B11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11">
+        <v>0.59850000000000003</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>400</v>
+      </c>
+      <c r="B12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12">
+        <v>0.66549999999999998</v>
+      </c>
+      <c r="D12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A32BB3E-378A-4905-8AAF-90259DF1A0AD}">
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>100</v>
+      </c>
+      <c r="B2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2">
+        <v>0.54649999999999999</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>46202</v>
+      </c>
+      <c r="H2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>200</v>
+      </c>
+      <c r="B3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3">
+        <v>0.58750000000000002</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>300</v>
+      </c>
+      <c r="B4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C4">
+        <v>0.60350000000000004</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>400</v>
+      </c>
+      <c r="B5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5">
+        <v>0.59850000000000003</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>500</v>
+      </c>
+      <c r="B6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6">
+        <v>0.61250000000000004</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>600</v>
+      </c>
+      <c r="B7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7">
+        <v>0.61550000000000005</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>700</v>
+      </c>
+      <c r="B8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8">
+        <v>0.61950000000000005</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>800</v>
+      </c>
+      <c r="B9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C9">
+        <v>0.63</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>900</v>
+      </c>
+      <c r="B10" t="s">
+        <v>101</v>
+      </c>
+      <c r="C10">
+        <v>0.61399999999999999</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1000</v>
+      </c>
+      <c r="B11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C11">
+        <v>0.63749999999999996</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2">
+        <v>46202</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>